--- a/Result/profitability/2363.xlsx
+++ b/Result/profitability/2363.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3912499999999999</v>
+        <v>0.2125</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>30.3025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1575</v>
+        <v>0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>30.39375</v>
+        <v>30.0775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1975</v>
+        <v>0.20125</v>
       </c>
       <c r="N4" t="n">
-        <v>31.1825</v>
+        <v>29.11</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>-4.37</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.34875</v>
+        <v>-0.495</v>
       </c>
       <c r="N5" t="n">
-        <v>30.135</v>
+        <v>29.695</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.49625</v>
+        <v>-0.525</v>
       </c>
       <c r="N6" t="n">
-        <v>31.41625</v>
+        <v>31.535</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.50875</v>
+        <v>-0.51375</v>
       </c>
       <c r="N7" t="n">
-        <v>33.215</v>
+        <v>33.30875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.47</v>
+        <v>-0.4875</v>
       </c>
       <c r="N8" t="n">
-        <v>34.78125</v>
+        <v>34.6925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.47375</v>
+        <v>-0.4737499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>35.8575</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D75" t="n">
+        <v>835</v>
+      </c>
+      <c r="E75" t="n">
+        <v>326</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>15</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3949999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.4825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8235294117647058</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7100000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02466134074331372</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.975</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.520000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1113924050632912</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
